--- a/gaming_forms/006_social_gaming_feedback_survey--gaming_forms.xlsx
+++ b/gaming_forms/006_social_gaming_feedback_survey--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'twitch'}</t>
+          <t>twitch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Twitch'}</t>
+          <t>Twitch</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'reddit'}</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Reddit'}</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'discord'}</t>
+          <t>discord</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Discord'}</t>
+          <t>Discord</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Two'}</t>
+          <t>Two</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'three'}</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Three'}</t>
+          <t>Three</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Two'}</t>
+          <t>Two</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'three'}</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Three'}</t>
+          <t>Three</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Two'}</t>
+          <t>Two</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'three'}</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Three'}</t>
+          <t>Three</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'game_mechanics'}</t>
+          <t>game_mechanics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Game Mechanics'}</t>
+          <t>Game Mechanics</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'game_strategies'}</t>
+          <t>game_strategies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Game Strategies'}</t>
+          <t>Game Strategies</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'game_setting'}</t>
+          <t>game_setting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Game Setting'}</t>
+          <t>Game Setting</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Other (Please specify)'}</t>
+          <t>Other (Please specify)</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'not_important_at_all'}</t>
+          <t>not_important_at_all</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important at All'}</t>
+          <t>Not Important at All</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'not_important_at_all'}</t>
+          <t>not_important_at_all</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important at All'}</t>
+          <t>Not Important at All</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'not_important_at_all'}</t>
+          <t>not_important_at_all</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important at All'}</t>
+          <t>Not Important at All</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'not_important_at_all'}</t>
+          <t>not_important_at_all</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Not Important at All'}</t>
+          <t>Not Important at All</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Java'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'python'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Python'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Other (Please specify)'}</t>
+          <t>Other (Please specify)</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Java'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Other (Please specify)'}</t>
+          <t>Other (Please specify)</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'unity'}</t>
+          <t>unity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Unity'}</t>
+          <t>Unity</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'unreal_engine'}</t>
+          <t>unreal_engine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Unreal Engine'}</t>
+          <t>Unreal Engine</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'godot'}</t>
+          <t>godot</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Godot'}</t>
+          <t>Godot</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'cocos2d-x'}</t>
+          <t>cocos2d-x</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Cocos2d-x'}</t>
+          <t>Cocos2d-x</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'c#'}</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'C#'}</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
